--- a/0001_ROBOS/CAPTAÇÃO/GSC E SM BAIXA/sm.xlsx
+++ b/0001_ROBOS/CAPTAÇÃO/GSC E SM BAIXA/sm.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5312,6 +5312,1858 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Rosana Del Rey da Silva Santos</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>76383793</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F133" s="1" t="n">
+        <v>31167</v>
+      </c>
+      <c r="G133" t="n">
+        <v>13366810718</v>
+      </c>
+      <c r="H133" t="n">
+        <v>21993480662</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>christian roberto ferreira de lima</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>95963186</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AES Tijuca</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>95963186</v>
+      </c>
+      <c r="G134" t="n">
+        <v>95963186</v>
+      </c>
+      <c r="H134" t="n">
+        <v>95963186</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>rosangela da costa barbosa</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>95881001</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AES Botafogo</t>
+        </is>
+      </c>
+      <c r="F135" s="1" t="n">
+        <v>29585</v>
+      </c>
+      <c r="G135" t="n">
+        <v>8224114740</v>
+      </c>
+      <c r="H135" t="n">
+        <v>21986959175</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>JULIO CEZAR PEREIRA</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>760959501</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AES Campo Grande</t>
+        </is>
+      </c>
+      <c r="F136" s="1" t="n">
+        <v>23998</v>
+      </c>
+      <c r="G136" t="n">
+        <v>90801180791</v>
+      </c>
+      <c r="H136" t="n">
+        <v>21986384899</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>CECILIA GOMES DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>94458917</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AES Campo Grande</t>
+        </is>
+      </c>
+      <c r="F137" s="1" t="n">
+        <v>33786</v>
+      </c>
+      <c r="G137" t="n">
+        <v>6129667710</v>
+      </c>
+      <c r="H137" t="n">
+        <v>21992180912</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>LUCIA HELENA DE SOUZA SANTOS</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>436807033</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D138" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AES Campo Grande</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="n">
+        <v>21373</v>
+      </c>
+      <c r="G138" t="n">
+        <v>5397109703</v>
+      </c>
+      <c r="H138" t="n">
+        <v>21995163041</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Nata Correa Nunes</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>92675404</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F139" s="1" t="n">
+        <v>37599</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1783586876</v>
+      </c>
+      <c r="H139" t="n">
+        <v>2198185241</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>THAIS SANTOS DOMINGUES</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>89053481</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D140" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AES Campo Grande</t>
+        </is>
+      </c>
+      <c r="F140" s="1" t="n">
+        <v>32653</v>
+      </c>
+      <c r="G140" t="n">
+        <v>11745764720</v>
+      </c>
+      <c r="H140" t="n">
+        <v>21994135392</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>EDUARDA SOARES DA SILVA DAMASIO</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>95259259</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D141" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AES Campo Grande</t>
+        </is>
+      </c>
+      <c r="F141" s="1" t="n">
+        <v>36803</v>
+      </c>
+      <c r="G141" t="n">
+        <v>13748419783</v>
+      </c>
+      <c r="H141" t="n">
+        <v>21994017859</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>jose fernando bispo da silva</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>97394511</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D142" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AES Caxias</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>21/041953</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>50995547883</v>
+      </c>
+      <c r="H142" t="n">
+        <v>21</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>patricia de souza lima</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>84931252</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D143" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F143" s="1" t="n">
+        <v>36528</v>
+      </c>
+      <c r="G143" t="n">
+        <v>12192299702</v>
+      </c>
+      <c r="H143" t="n">
+        <v>21969541211</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>rosenei silva souza milagres</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>94144378</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D144" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AES Botafogo</t>
+        </is>
+      </c>
+      <c r="F144" s="1" t="n">
+        <v>27758</v>
+      </c>
+      <c r="G144" t="n">
+        <v>3447356642</v>
+      </c>
+      <c r="H144" t="n">
+        <v>24992619339</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>vanessa galiotto girardi</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>21969411149</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D145" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AES Botafogo</t>
+        </is>
+      </c>
+      <c r="F145" s="1" t="n">
+        <v>30709</v>
+      </c>
+      <c r="G145" t="n">
+        <v>10381409783</v>
+      </c>
+      <c r="H145" t="n">
+        <v>21969411149</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>vanessa galiotto girard</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>93840417</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D146" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AES Botafogo</t>
+        </is>
+      </c>
+      <c r="F146" s="1" t="n">
+        <v>30709</v>
+      </c>
+      <c r="G146" t="n">
+        <v>10381409783</v>
+      </c>
+      <c r="H146" t="n">
+        <v>21969411149</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>luciane tiago simao ferreira</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>96969546</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D147" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F147" s="1" t="n">
+        <v>26287</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2735584712</v>
+      </c>
+      <c r="H147" t="n">
+        <v>21996498868</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Denise de souza</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>96723722</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D148" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AES Caxias</t>
+        </is>
+      </c>
+      <c r="F148" s="1" t="n">
+        <v>30540</v>
+      </c>
+      <c r="G148" t="n">
+        <v>9343461780</v>
+      </c>
+      <c r="H148" t="n">
+        <v>21974632265</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Ivanir de araujo do vale</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>95090573</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D149" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AES Caxias</t>
+        </is>
+      </c>
+      <c r="F149" s="1" t="n">
+        <v>22984</v>
+      </c>
+      <c r="G149" t="n">
+        <v>90975316753</v>
+      </c>
+      <c r="H149" t="n">
+        <v>21991339151</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Tatiane rocha araujo</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>85576597</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D150" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AES Caxias</t>
+        </is>
+      </c>
+      <c r="F150" s="1" t="n">
+        <v>29742</v>
+      </c>
+      <c r="G150" t="n">
+        <v>9254290742</v>
+      </c>
+      <c r="H150" t="n">
+        <v>21974221150</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>isaac rezende de almeida silva</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>97507658</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AES Campo Grande</t>
+        </is>
+      </c>
+      <c r="F151" s="1" t="n">
+        <v>40004</v>
+      </c>
+      <c r="G151" t="n">
+        <v>17678962711</v>
+      </c>
+      <c r="H151" t="n">
+        <v>21967506007</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>tiago ferreira da silva</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>86676935</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AES Guarulhos</t>
+        </is>
+      </c>
+      <c r="F152" s="1" t="n">
+        <v>33005</v>
+      </c>
+      <c r="G152" t="n">
+        <v>38122548830</v>
+      </c>
+      <c r="H152" t="n">
+        <v>1124131867</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>flavio nacle de campos</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>92619007</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D153" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F153" s="1" t="n">
+        <v>32765</v>
+      </c>
+      <c r="G153" t="n">
+        <v>12618324773</v>
+      </c>
+      <c r="H153" t="n">
+        <v>21966177320</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>jandira anacleto da silva</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>89345868</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D154" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AES Tijuca</t>
+        </is>
+      </c>
+      <c r="F154" s="1" t="n">
+        <v>27444</v>
+      </c>
+      <c r="G154" t="n">
+        <v>5667023717</v>
+      </c>
+      <c r="H154" t="n">
+        <v>21989585622</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>heloisa maria rangel de goes</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>96014767</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D155" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AES Tijuca</t>
+        </is>
+      </c>
+      <c r="F155" s="1" t="n">
+        <v>27384</v>
+      </c>
+      <c r="G155" t="n">
+        <v>2419630793</v>
+      </c>
+      <c r="H155" t="n">
+        <v>21999439363</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>eduardo martins dos santos</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>89596633</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D156" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AES Tijuca</t>
+        </is>
+      </c>
+      <c r="F156" s="1" t="n">
+        <v>34645</v>
+      </c>
+      <c r="G156" t="n">
+        <v>5188683113</v>
+      </c>
+      <c r="H156" t="n">
+        <v>21972209134</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>alessandra das chagas monteiro dos santos</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>87560577</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F157" s="1" t="n">
+        <v>29047</v>
+      </c>
+      <c r="G157" t="n">
+        <v>8691289732</v>
+      </c>
+      <c r="H157" t="n">
+        <v>21993420864</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>alessandra das chagas monteiro dos santos</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>87560577</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F158" s="1" t="n">
+        <v>29047</v>
+      </c>
+      <c r="G158" t="n">
+        <v>8691289732</v>
+      </c>
+      <c r="H158" t="n">
+        <v>21993420864</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>elizabeth nunes de lima</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>89899267</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AES Guarulhos</t>
+        </is>
+      </c>
+      <c r="F159" s="1" t="n">
+        <v>27297</v>
+      </c>
+      <c r="G159" t="n">
+        <v>16044997880</v>
+      </c>
+      <c r="H159" t="n">
+        <v>11992334376</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Lorena Nunes Braz Maia</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>93686308</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F160" s="1" t="n">
+        <v>35055</v>
+      </c>
+      <c r="G160" t="n">
+        <v>15856041780</v>
+      </c>
+      <c r="H160" t="n">
+        <v>21979447630</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Bruna Medeiros Aguilera Vernek</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>81808910</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F161" s="1" t="n">
+        <v>34255</v>
+      </c>
+      <c r="G161" t="n">
+        <v>15444674785</v>
+      </c>
+      <c r="H161" t="n">
+        <v>21980105075</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Maria Jose do Nascimento Alves</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>82419449</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F162" s="1" t="n">
+        <v>19617</v>
+      </c>
+      <c r="G162" t="n">
+        <v>12649400765</v>
+      </c>
+      <c r="H162" t="n">
+        <v>2199148252</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>laelso dos santos salomao</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>95879928</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AES Tijuca</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>95879928</v>
+      </c>
+      <c r="G163" t="n">
+        <v>95879928</v>
+      </c>
+      <c r="H163" t="n">
+        <v>95879928</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Fellipe Gil Pereira da Silva</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>95305224</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D164" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F164" s="1" t="n">
+        <v>33501</v>
+      </c>
+      <c r="G164" t="n">
+        <v>10464831709</v>
+      </c>
+      <c r="H164" t="n">
+        <v>21972355650</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>angela garcia de souza</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>76610486</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>UA Luz Butantã</t>
+        </is>
+      </c>
+      <c r="F165" s="1" t="n">
+        <v>25116</v>
+      </c>
+      <c r="G165" t="n">
+        <v>10078669855</v>
+      </c>
+      <c r="H165" t="n">
+        <v>11994718055</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>julia ogando mendonca</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>95609610</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AES Tijuca</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>95609610</v>
+      </c>
+      <c r="G166" t="n">
+        <v>95609610</v>
+      </c>
+      <c r="H166" t="n">
+        <v>95609610</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>PLACIDO FERREIRA FERNANDES</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>95309384</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AES Campo Grande</t>
+        </is>
+      </c>
+      <c r="F167" s="1" t="n">
+        <v>30008</v>
+      </c>
+      <c r="G167" t="n">
+        <v>9941556709</v>
+      </c>
+      <c r="H167" t="n">
+        <v>21972279953</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Suria Iohanna Cerino Cordeiro</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>95686114</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F168" s="1" t="n">
+        <v>41085</v>
+      </c>
+      <c r="G168" t="n">
+        <v>16822680713</v>
+      </c>
+      <c r="H168" t="n">
+        <v>21990030621</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ana luisa ferreira da silva</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>95570885</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AES Caxias</t>
+        </is>
+      </c>
+      <c r="F169" s="1" t="n">
+        <v>37676</v>
+      </c>
+      <c r="G169" t="n">
+        <v>15889249711</v>
+      </c>
+      <c r="H169" t="n">
+        <v>21965021427</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>CARLA CRISTINA FERREIRA DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>96156875</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D170" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AES Campo Grande</t>
+        </is>
+      </c>
+      <c r="F170" s="1" t="n">
+        <v>37581</v>
+      </c>
+      <c r="G170" t="n">
+        <v>9473197780</v>
+      </c>
+      <c r="H170" t="n">
+        <v>21989546094</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>judith lacerda da silva</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>450391639</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AES Tatuapé</t>
+        </is>
+      </c>
+      <c r="F171" s="1" t="n">
+        <v>15786</v>
+      </c>
+      <c r="G171" t="n">
+        <v>8595484813</v>
+      </c>
+      <c r="H171" t="n">
+        <v>11982729154</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>vanessa batista viana</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>97051509</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AES Tatuapé</t>
+        </is>
+      </c>
+      <c r="F172" s="1" t="n">
+        <v>27719</v>
+      </c>
+      <c r="G172" t="n">
+        <v>15788161819</v>
+      </c>
+      <c r="H172" t="n">
+        <v>11975006310</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>cleiton de lima barroso</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>93232575</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D173" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AES Campo Grande</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>93232575</v>
+      </c>
+      <c r="G173" t="n">
+        <v>93232575</v>
+      </c>
+      <c r="H173" t="n">
+        <v>93232575</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>iara suzan nascimento silva</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>87919580</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D174" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AES Guarulhos</t>
+        </is>
+      </c>
+      <c r="F174" s="1" t="n">
+        <v>33572</v>
+      </c>
+      <c r="G174" t="n">
+        <v>40315840838</v>
+      </c>
+      <c r="H174" t="n">
+        <v>11948411296</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>josemar dos santos martins</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>594344468</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D175" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AES Guarulhos</t>
+        </is>
+      </c>
+      <c r="F175" s="1" t="n">
+        <v>31770</v>
+      </c>
+      <c r="G175" t="n">
+        <v>35227173842</v>
+      </c>
+      <c r="H175" t="n">
+        <v>11951748184</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>andrea jesus da paz</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>95147767</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AES Caxias</t>
+        </is>
+      </c>
+      <c r="F176" s="1" t="n">
+        <v>28807</v>
+      </c>
+      <c r="G176" t="n">
+        <v>5268124781</v>
+      </c>
+      <c r="H176" t="n">
+        <v>21979863099</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Francisco de assis alves medeiro</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>79235592</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AES Tijuca</t>
+        </is>
+      </c>
+      <c r="F177" s="1" t="n">
+        <v>22413</v>
+      </c>
+      <c r="G177" t="n">
+        <v>63571110749</v>
+      </c>
+      <c r="H177" t="n">
+        <v>21999921227</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ana carolina de o rebelo</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>89209188</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D178" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AES Tijuca</t>
+        </is>
+      </c>
+      <c r="F178" s="1" t="n">
+        <v>36743</v>
+      </c>
+      <c r="G178" t="n">
+        <v>16586682789</v>
+      </c>
+      <c r="H178" t="n">
+        <v>21968358152</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>sirlande sa santos</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>97029277</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D179" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>UA Luz Butantã</t>
+        </is>
+      </c>
+      <c r="F179" s="1" t="n">
+        <v>31439</v>
+      </c>
+      <c r="G179" t="n">
+        <v>35624179855</v>
+      </c>
+      <c r="H179" t="n">
+        <v>11916108634</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>bruno alves calazans</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>759046638</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F180" s="1" t="n">
+        <v>39204</v>
+      </c>
+      <c r="G180" t="n">
+        <v>16402827770</v>
+      </c>
+      <c r="H180" t="n">
+        <v>21980963584</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>samara grusman ferraz</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>94995314</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F181" s="1" t="n">
+        <v>39578</v>
+      </c>
+      <c r="G181" t="n">
+        <v>14768024750</v>
+      </c>
+      <c r="H181" t="n">
+        <v>21967514328</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Sthefany Grusman Ferraz</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>94995313</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Baixa Complexidade</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AES Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="F182" s="1" t="n">
+        <v>38793</v>
+      </c>
+      <c r="G182" t="n">
+        <v>16653650723</v>
+      </c>
+      <c r="H182" t="n">
+        <v>2174800511</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>enviado captação</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
